--- a/data/trans_camb/IP1018-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Clase-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,0</t>
+          <t>-1,63; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,54</t>
+          <t>-0,99; 0,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,0</t>
+          <t>-0,81; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,0</t>
+          <t>-4,82; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,0</t>
+          <t>-5,79; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 0,0</t>
+          <t>-5,72; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 0,0</t>
+          <t>-6,36; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,51; -0,35</t>
+          <t>-3,59; -0,36</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,77; -0,36</t>
+          <t>-3,49; -0,36</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,0</t>
+          <t>-0,75; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,46</t>
+          <t>-0,42; 0,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,55</t>
+          <t>-0,29; 0,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; -0,05</t>
+          <t>-0,43; -0,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,38</t>
+          <t>-0,23; 0,37</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,92; 677,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Clase-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,55</t>
+          <t>-0,99; 0,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,0</t>
+          <t>-0,82; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,55</t>
+          <t>-0,36; 0,55</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,18</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,0</t>
+          <t>-5,3; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 0,0</t>
+          <t>-5,3; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 0,0</t>
+          <t>-5,57; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,0</t>
+          <t>-5,99; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,36</t>
+          <t>-3,63; -0,35</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,49; -0,36</t>
+          <t>-3,53; -0,35</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,0</t>
+          <t>-0,76; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,44</t>
+          <t>-0,45; 0,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,0</t>
+          <t>-0,6; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,55</t>
+          <t>-0,34; 0,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; -0,05</t>
+          <t>-0,47; -0,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,37</t>
+          <t>-0,23; 0,4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,92; 677,35</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,77</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,06</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,54</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,81; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>-1,06; 0,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,0</t>
+          <t>-0,98; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,55</t>
+          <t>-0,35; 0,55</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-17,06%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0,76</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,43</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-0,96</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-0,96</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,0</t>
+          <t>-5,76; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,0</t>
+          <t>-5,68; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,0</t>
+          <t>-4,83; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 0,0</t>
+          <t>-4,83; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,63; -0,35</t>
+          <t>-3,51; -0,35</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,53; -0,35</t>
+          <t>-3,77; -0,36</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,18</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,05</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,21</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,06</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,0</t>
+          <t>-0,68; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,45</t>
+          <t>-0,31; 0,55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,0</t>
+          <t>-0,74; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,56</t>
+          <t>-0,43; 0,46</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; -0,05</t>
+          <t>-0,49; -0,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,4</t>
+          <t>-0,22; 0,38</t>
         </is>
       </c>
     </row>
@@ -1610,17 +1610,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>29,93%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>26,37%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>29,93%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
